--- a/content/W01/D3/demos/C2_W01_D03_decision_tool_STUDENT.xlsx
+++ b/content/W01/D3/demos/C2_W01_D03_decision_tool_STUDENT.xlsx
@@ -490,14 +490,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Which Q1 figure is right: the decision tool</t>
+          <t>Which four cleaning decisions get the export to the books?</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Kalpa Retail, Week 1, Wednesday. Four cleaning decisions the day taught, one tab each, and an Export tab that assembles the note to Anand.</t>
+          <t>Kalpa Retail, Week 1, Wednesday. Anand Iyer, the finance controller, acts only on a figure that matches his books to the rupee, and his analyst ties out every figure, matching it to the books line by line. Four cleaning decisions the day taught get an export there, one tab each, and an Export tab assembles the note.</t>
         </is>
       </c>
     </row>
@@ -593,7 +593,7 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>2400</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="B5">
@@ -835,7 +835,7 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>2400</v>
+        <v>2500</v>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
@@ -879,7 +879,7 @@
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>2400</v>
+        <v>2500</v>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Keep the large order?</t>
+          <t>Should the large order stay in revenue?</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Rows and rupees, to the books</t>
+          <t>Do rows and rupees both tie to the books?</t>
         </is>
       </c>
     </row>
@@ -1469,7 +1469,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>The note, assembled</t>
+          <t>Is the note to Anand ready to paste?</t>
         </is>
       </c>
     </row>

--- a/content/W01/D3/demos/C2_W01_D03_decision_tool_STUDENT.xlsx
+++ b/content/W01/D3/demos/C2_W01_D03_decision_tool_STUDENT.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Start" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profile" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Identity" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tail" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Largest" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reconcile" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Export" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
@@ -525,7 +525,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Profile: what converts. Identity: what makes two rows one order. Tail: keep the large order. Reconcile: rows and rupees.</t>
+          <t>The Profile tab counts what converts, the Identity tab says what makes two rows one order, the Largest tab keeps a large order that is real, and the Reconcile tab ties rows and rupees to the books.</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Eight invented Business orders. A fence flags the tail for checking; it never removes real revenue.</t>
+          <t>Eight invented Business orders. A fence flags the largest for a check of their records, and revenue keeps every valid order.</t>
         </is>
       </c>
     </row>
@@ -1278,7 +1278,7 @@
         </is>
       </c>
       <c r="E13" s="8">
-        <f>IF(E9&lt;&gt;E8,"Fix the revenue that drops the tail before reporting it.","Keep all "&amp;COUNT(A5:A12)&amp;" orders, "&amp;"Rs "&amp;IF(ROUND(E8,0)&gt;=100000,INT(ROUND(E8,0)/100000)&amp;","&amp;TEXT(INT(MOD(ROUND(E8,0),100000)/1000),"00")&amp;","&amp;TEXT(MOD(ROUND(E8,0),1000),"000"),IF(ROUND(E8,0)&gt;=1000,INT(ROUND(E8,0)/1000)&amp;","&amp;TEXT(MOD(ROUND(E8,0),1000),"000"),ROUND(E8,0)&amp;""))&amp;"; flag "&amp;E10&amp;" above the fence for a record check, and show the total without "&amp;IF(E10=1,"it","them")&amp;" beside it.")</f>
+        <f>IF(E9&lt;&gt;E8,"Fix the revenue that drops the largest orders before reporting it.","Keep all "&amp;COUNT(A5:A12)&amp;" orders, "&amp;"Rs "&amp;IF(ROUND(E8,0)&gt;=100000,INT(ROUND(E8,0)/100000)&amp;","&amp;TEXT(INT(MOD(ROUND(E8,0),100000)/1000),"00")&amp;","&amp;TEXT(MOD(ROUND(E8,0),1000),"000"),IF(ROUND(E8,0)&gt;=1000,INT(ROUND(E8,0)/1000)&amp;","&amp;TEXT(MOD(ROUND(E8,0),1000),"000"),ROUND(E8,0)&amp;""))&amp;"; flag "&amp;E10&amp;" above the fence for a record check, and show the total without "&amp;IF(E10=1,"it","them")&amp;" beside it.")</f>
         <v/>
       </c>
     </row>
@@ -1476,7 +1476,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Released only when every tab's check passes. Paste it into the note to Anand.</t>
+          <t>The note below is released only when every tab's check passes, and then it pastes into the note to Anand.</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
         </is>
       </c>
       <c r="B4">
-        <f>Profile!E12+Identity!B21+Tail!E14+Reconcile!B14</f>
+        <f>Profile!E12+Identity!B21+Largest!E14+Reconcile!B14</f>
         <v/>
       </c>
     </row>
@@ -1509,7 +1509,7 @@
         </is>
       </c>
       <c r="B7" s="2">
-        <f>IF(B4=4,"Profile: "&amp;Profile!E11&amp;CHAR(10)&amp;"Identity: "&amp;Identity!B20&amp;CHAR(10)&amp;"Tail: "&amp;Tail!E13&amp;CHAR(10)&amp;"Reconcile: "&amp;Reconcile!B13,"The note assembles once every tab passes its check.")</f>
+        <f>IF(B4=4,"Profile: "&amp;Profile!E11&amp;CHAR(10)&amp;"Identity: "&amp;Identity!B20&amp;CHAR(10)&amp;"Largest order: "&amp;Largest!E13&amp;CHAR(10)&amp;"Reconcile: "&amp;Reconcile!B13,"The note assembles once every tab passes its check.")</f>
         <v/>
       </c>
     </row>

--- a/content/W01/D3/demos/C2_W01_D03_decision_tool_STUDENT.xlsx
+++ b/content/W01/D3/demos/C2_W01_D03_decision_tool_STUDENT.xlsx
@@ -563,7 +563,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Ten invented amounts as the file holds them, as text. A failure is counted and logged, never turned into a number.</t>
+          <t>Ten invented amounts as the file holds them, as text. A failure is logged, never turned into a number.</t>
         </is>
       </c>
     </row>
